--- a/output/topology_excel/4698.xlsx
+++ b/output/topology_excel/4698.xlsx
@@ -487,7 +487,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -509,7 +509,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -531,7 +531,7 @@
         <v>1</v>
       </c>
       <c r="B5" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -550,10 +550,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="B6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -575,7 +575,7 @@
         <v>3</v>
       </c>
       <c r="B7" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -594,10 +594,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B8" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -616,10 +616,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B9" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -638,10 +638,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -660,10 +660,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B11" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -682,10 +682,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -729,7 +729,7 @@
         <v>1</v>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -751,7 +751,7 @@
         <v>1</v>
       </c>
       <c r="B15" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -773,7 +773,7 @@
         <v>2</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>2</v>
       </c>
       <c r="B17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -817,7 +817,7 @@
         <v>3</v>
       </c>
       <c r="B18" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -839,7 +839,7 @@
         <v>3</v>
       </c>
       <c r="B19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -850,18 +850,18 @@
         <v>1</v>
       </c>
       <c r="E19" t="n">
-        <v>109</v>
+        <v>377</v>
       </c>
       <c r="F19" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B20" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -872,18 +872,18 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>153</v>
+        <v>99</v>
       </c>
       <c r="F20" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -894,7 +894,7 @@
         <v>1</v>
       </c>
       <c r="E21" t="n">
-        <v>99</v>
+        <v>165</v>
       </c>
       <c r="F21" t="n">
         <v>13</v>
@@ -902,7 +902,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B22" t="n">
         <v>8</v>
@@ -916,18 +916,18 @@
         <v>1</v>
       </c>
       <c r="E22" t="n">
-        <v>111</v>
+        <v>203</v>
       </c>
       <c r="F22" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B23" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -938,18 +938,18 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>117</v>
+        <v>153</v>
       </c>
       <c r="F23" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B24" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -960,10 +960,10 @@
         <v>1</v>
       </c>
       <c r="E24" t="n">
-        <v>377</v>
+        <v>169</v>
       </c>
       <c r="F24" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
     </row>
     <row r="25">
@@ -971,7 +971,7 @@
         <v>5</v>
       </c>
       <c r="B25" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -982,10 +982,10 @@
         <v>1</v>
       </c>
       <c r="E25" t="n">
-        <v>203</v>
+        <v>47</v>
       </c>
       <c r="F25" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="26">
@@ -1004,10 +1004,10 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>169</v>
+        <v>117</v>
       </c>
       <c r="F26" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
     </row>
     <row r="27">
@@ -1015,7 +1015,7 @@
         <v>6</v>
       </c>
       <c r="B27" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>1</v>
       </c>
       <c r="E27" t="n">
-        <v>47</v>
+        <v>165</v>
       </c>
       <c r="F27" t="n">
         <v>13</v>
@@ -1037,7 +1037,7 @@
         <v>7</v>
       </c>
       <c r="B28" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -1048,7 +1048,7 @@
         <v>1</v>
       </c>
       <c r="E28" t="n">
-        <v>165</v>
+        <v>111</v>
       </c>
       <c r="F28" t="n">
         <v>13</v>
@@ -1056,10 +1056,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B29" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -1070,10 +1070,10 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>165</v>
+        <v>147</v>
       </c>
       <c r="F29" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
     </row>
     <row r="30">
@@ -1092,10 +1092,10 @@
         <v>1</v>
       </c>
       <c r="E30" t="n">
-        <v>147</v>
+        <v>109</v>
       </c>
       <c r="F30" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>

--- a/output/topology_excel/4698.xlsx
+++ b/output/topology_excel/4698.xlsx
@@ -451,12 +451,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Length</t>
+          <t>Length_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Width</t>
+          <t>Width_1</t>
         </is>
       </c>
     </row>
